--- a/samples/fake_year_1_grades_sample.xlsx
+++ b/samples/fake_year_1_grades_sample.xlsx
@@ -983,7 +983,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <v>49</v>
